--- a/DateBase/orders/Nhat 48_2026-3-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-5.xlsx
@@ -609,6 +609,9 @@
       <c r="C21" t="str">
         <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -667,7 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0106108612910101010152515105515100</v>
+        <v>0106108612910101010152515105515105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-5.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -613,9 +613,25 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -670,7 +686,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0106108612910101010152515105515105</v>
+        <v>01061086129101010101525151055151051010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-5.xlsx
@@ -688,6 +688,9 @@
       <c r="G2" t="str">
         <v>01061086129101010101525151055151051010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
